--- a/DataTables/Datas/__beans__.xlsx
+++ b/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaboom\Downloads\Lcc-master\Lcc-master\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9AF3CF-3FF4-4E35-AF03-060C6B6B4C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC6C0AA-F9BE-4210-A2C8-A839F3A507A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -90,27 +90,6 @@
   </si>
   <si>
     <t>注释</t>
-  </si>
-  <si>
-    <t>TBBuffValue</t>
-  </si>
-  <si>
-    <t>buff</t>
-  </si>
-  <si>
-    <t>ValuePropertyType</t>
-  </si>
-  <si>
-    <t>值属性类型</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>值</t>
   </si>
   <si>
     <t>TBReward</t>
@@ -531,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -587,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
         <v>11</v>
@@ -602,7 +581,7 @@
         <v>8</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -619,7 +598,7 @@
         <v>15</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
@@ -631,67 +610,38 @@
         <v>18</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="J4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N4" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N5" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
